--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table08.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table08.xlsx
@@ -118,7 +118,7 @@
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="0_)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -127,12 +127,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="4"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -198,6 +192,19 @@
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="4"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -247,66 +254,78 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -815,28 +834,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2187,16 +2206,16 @@
       <c r="H53" s="6"/>
     </row>
     <row r="54" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="24"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1">
       <c r="A55" s="9" t="s">
@@ -2445,9 +2464,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.196850393700787" bottom="0.196850393700787" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="60" orientation="portrait" horizontalDpi="300"/>
+  <pageSetup paperSize="9" scale="60" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>